--- a/termine.xlsx
+++ b/termine.xlsx
@@ -1,21 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Debian\home\karin\private\almstueberlmusi.at\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B44189D5-63E3-40EE-89AF-8600AD019148}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="7"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10404" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabellenblatt1" sheetId="1" r:id="rId1"/>
+    <sheet name="Tabellenblatt1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -25,199 +20,222 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="53">
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>location</t>
-  </si>
-  <si>
-    <t>details</t>
-  </si>
-  <si>
-    <t>url</t>
-  </si>
-  <si>
-    <t>94209 Regen; Bayern</t>
-  </si>
-  <si>
-    <t>drumherum – Das Volksmusikspektakel</t>
-  </si>
-  <si>
-    <t>https://www.drumherum.com/teilnehmer/musikanten/teilnehmer-2024-98.html?gruppe=0226</t>
-  </si>
-  <si>
-    <t>5524 Annaberg im Lammertal</t>
-  </si>
-  <si>
-    <t>Rottenhofhütte</t>
-  </si>
-  <si>
-    <t>https://www.rottenhofhuette.at/</t>
-  </si>
-  <si>
-    <t>5020 Salzburg</t>
-  </si>
-  <si>
-    <t>Salzburger Straßenmusik</t>
-  </si>
-  <si>
-    <t>https://www.salzburgervolksliedwerk.at/fileadmin/user_upload/volksliedwerk/user_upload/Folder_Salzburger_Strassenmusik_2024_web.pdf</t>
-  </si>
-  <si>
-    <t>8966 Aich</t>
-  </si>
-  <si>
-    <t>Aicher Kirchtag</t>
-  </si>
-  <si>
-    <t>https://www.aicher-herbst-kultur.at/Aicher_Kirtag/</t>
-  </si>
-  <si>
-    <t>5524 Annaberg im Lammertal; Winterstellgut</t>
-  </si>
-  <si>
-    <t>Hochzeit (privat)</t>
-  </si>
-  <si>
-    <t>https://www.tauroa.at/de/winterstellgut/</t>
-  </si>
-  <si>
-    <t>5453 Werfenweng</t>
-  </si>
-  <si>
-    <t>Werfenwenger Weis</t>
-  </si>
-  <si>
-    <t>https://www.salzburgerland.com/de/werfenweng/veranstaltungen/SBG/ff809fc9-ee1b-4036-82a1-35f154d0332f/werfenwenger-herbst-weis</t>
-  </si>
-  <si>
-    <t>5620 Schwarzach im Pongau</t>
-  </si>
-  <si>
-    <t>Weihnachtsfeier</t>
-  </si>
-  <si>
-    <t>https://www.gde-schwarzach.salzburg.at/Seniorenzentrum_Schwarzach</t>
-  </si>
-  <si>
-    <t>5451 Tenneck</t>
-  </si>
-  <si>
-    <t>Adventkonzert</t>
-  </si>
-  <si>
-    <t>https://www.salzburgervolksliedwerk.at/termine/detail?tx_calendarize_calendar%5Baction%5D=detail&amp;tx_calendarize_calendar%5Bcontroller%5D=Calendar&amp;tx_calendarize_calendar%5Bindex%5D=103822&amp;cHash=3b0ade89f12374e9bdde86e47b10ff89</t>
-  </si>
-  <si>
-    <t>5611 Großarl</t>
-  </si>
-  <si>
-    <t>Alm-Musi-Roas: Rottenhofhütte</t>
-  </si>
-  <si>
-    <t>https://www.dachstein.at/de/aktuelles/events/alm-musi-roas</t>
-  </si>
-  <si>
-    <t>5542 Flachau</t>
-  </si>
-  <si>
-    <t>Stammgäste-Galaabend im Tirolerhof</t>
-  </si>
-  <si>
-    <t>https://www.hotel-tirolerhof.com/</t>
-  </si>
-  <si>
-    <t>5550 Radstadt</t>
-  </si>
-  <si>
-    <t>Erntedankfest</t>
-  </si>
-  <si>
-    <t>https://www.radstadt.com/radstadt/veranstaltungskalender/veranstaltungen/SPO/5daeaf0a-c467-4911-8642-9265a620dec0/roem--kath--erntedankfest-mit-prozession</t>
-  </si>
-  <si>
-    <t>Musikantenstammtisch</t>
-  </si>
-  <si>
-    <t>5661 Rauris</t>
-  </si>
-  <si>
-    <t>5500 Bischofshofen</t>
-  </si>
-  <si>
-    <t>5541 Altenmarkt-Zauchensee</t>
-  </si>
-  <si>
-    <t>Adventmarkt</t>
-  </si>
-  <si>
-    <t>https://www.altenmarkt-zauchensee.at/de/winter-urlaub/advent-markt.html</t>
-  </si>
-  <si>
-    <t>https://www.radstadt.at/Alpenlaendisches_Adventsingen</t>
-  </si>
-  <si>
-    <t>5450 Werfen</t>
-  </si>
-  <si>
-    <t>5700 Zell am See</t>
-  </si>
-  <si>
-    <t>Zeller Adventkonzert des KIWANIS Club Zell am See</t>
-  </si>
-  <si>
-    <t>https://www.zellamsee-kaprun.com/de/event/zeller-adventkonzert-des-kiwanis-club-zell-am-see~12225</t>
-  </si>
-  <si>
-    <t>Weihnachtswanderung</t>
-  </si>
-  <si>
-    <t>https://www.radstadt.com/radstadt/top-events/weihnachts-wanderungen/</t>
-  </si>
-  <si>
-    <t>https://www.stadt-salzburg.at/kultur/volkskultur/salzburger-strassenmusik/</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="54">
+  <si>
+    <t xml:space="preserve">date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94209 Regen; Bayern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drumherum – Das Volksmusikspektakel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.drumherum.com/teilnehmer/musikanten/teilnehmer-2024-98.html?gruppe=0226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5524 Annaberg im Lammertal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rottenhofhütte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.rottenhofhuette.at/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5020 Salzburg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salzburger Straßenmusik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.salzburgervolksliedwerk.at/fileadmin/user_upload/volksliedwerk/user_upload/Folder_Salzburger_Strassenmusik_2024_web.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8966 Aich</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aicher Kirchtag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.aicher-herbst-kultur.at/Aicher_Kirtag/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5524 Annaberg im Lammertal; Winterstellgut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hochzeit (privat)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.tauroa.at/de/winterstellgut/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5453 Werfenweng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Werfenwenger Weis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.salzburgerland.com/de/werfenweng/veranstaltungen/SBG/ff809fc9-ee1b-4036-82a1-35f154d0332f/werfenwenger-herbst-weis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5620 Schwarzach im Pongau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weihnachtsfeier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.gde-schwarzach.salzburg.at/Seniorenzentrum_Schwarzach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5451 Tenneck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adventkonzert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.salzburgervolksliedwerk.at/termine/detail?tx_calendarize_calendar%5Baction%5D=detail&amp;tx_calendarize_calendar%5Bcontroller%5D=Calendar&amp;tx_calendarize_calendar%5Bindex%5D=103822&amp;cHash=3b0ade89f12374e9bdde86e47b10ff89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5611 Großarl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alm-Musi-Roas: Rottenhofhütte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.dachstein.at/de/aktuelles/events/alm-musi-roas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5542 Flachau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stammgäste-Galaabend im Tirolerhof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.hotel-tirolerhof.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5550 Radstadt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erntedankfest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.radstadt.com/radstadt/veranstaltungskalender/veranstaltungen/SPO/5daeaf0a-c467-4911-8642-9265a620dec0/roem--kath--erntedankfest-mit-prozession</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Musikantenstammtisch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5661 Rauris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5500 Bischofshofen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5541 Altenmarkt-Zauchensee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adventmarkt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.altenmarkt-zauchensee.at/de/winter-urlaub/advent-markt.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.radstadt.at/Alpenlaendisches_Adventsingen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5450 Werfen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5700 Zell am See</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zeller Adventkonzert des KIWANIS Club Zell am See</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.zellamsee-kaprun.com/de/event/zeller-adventkonzert-des-kiwanis-club-zell-am-see~12225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weihnachtswanderung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.radstadt.com/radstadt/top-events/weihnachts-wanderungen/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.stadt-salzburg.at/kultur/volkskultur/salzburger-strassenmusik/</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.dachstein.at/de/aktuelles/events/alm-musi-roas </t>
   </si>
   <si>
     <t xml:space="preserve">https://zellamsee.kiwanis.at/veranstaltungen/ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Werfner Adventsingen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -230,7 +248,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -238,44 +256,154 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  <cellStyleXfs count="21">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Link" xfId="1" builtinId="8"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+  <cellStyles count="7">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="*unknown*" xfId="20" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF1155CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -317,14 +445,14 @@
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -354,7 +482,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -378,7 +506,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -438,30 +566,29 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr defaultColWidth="12.5625" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="1"/>
-    <col min="2" max="2" width="34.88671875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="34.5546875" style="2" customWidth="1"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="34.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="34.56"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -475,8 +602,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="n">
         <v>45429</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -489,8 +616,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="n">
         <v>45450</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -503,8 +630,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="n">
         <v>45493</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -517,8 +644,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="n">
         <v>45542</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -531,8 +658,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="n">
         <v>45563</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -545,8 +672,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="n">
         <v>45583</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -559,8 +686,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="n">
         <v>45617</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -573,8 +700,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="n">
         <v>45641</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -584,8 +711,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="n">
         <v>45836</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -598,8 +725,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="n">
         <v>45836</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -609,8 +736,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="n">
         <v>45844</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -623,8 +750,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="n">
         <v>45909</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -637,8 +764,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="n">
         <v>45921</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -651,8 +778,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="n">
         <v>45920</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -662,8 +789,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="n">
         <v>45948</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -673,8 +800,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="n">
         <v>45955</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -684,8 +811,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="n">
         <v>45998</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -698,8 +825,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="n">
         <v>45998</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -712,8 +839,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="n">
         <v>46004</v>
       </c>
       <c r="B20" s="8" t="s">
@@ -723,8 +850,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="9">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="n">
         <v>46005</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -737,8 +864,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
         <v>46005</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -747,12 +874,12 @@
       <c r="C22" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="0" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="n">
         <v>46017</v>
       </c>
       <c r="B23" s="2" t="s">
@@ -761,12 +888,12 @@
       <c r="C23" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="0" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="n">
         <v>46207</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -775,12 +902,12 @@
       <c r="C24" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="0" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="n">
         <v>46208</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -793,8 +920,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="n">
         <v>46355</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -803,12 +930,12 @@
       <c r="C26" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="0" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="n">
         <v>46369</v>
       </c>
       <c r="B27" s="2" t="s">
@@ -821,21 +948,51 @@
         <v>52</v>
       </c>
     </row>
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="n">
+        <v>46364</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="n">
+        <v>46363</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29" s="0" t="s">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D10" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="D12" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="D25" r:id="rId10" xr:uid="{E90E9CA0-5FF7-44A9-9CF2-DC4518677DF6}"/>
-    <hyperlink ref="D27" r:id="rId11" xr:uid="{0F01FA12-B2F6-4F67-8CD1-043DCF313522}"/>
+    <hyperlink ref="D2" r:id="rId1" display="https://www.drumherum.com/teilnehmer/musikanten/teilnehmer-2024-98.html?gruppe=0226"/>
+    <hyperlink ref="D3" r:id="rId2" display="https://www.rottenhofhuette.at/"/>
+    <hyperlink ref="D4" r:id="rId3" display="https://www.salzburgervolksliedwerk.at/fileadmin/user_upload/volksliedwerk/user_upload/Folder_Salzburger_Strassenmusik_2024_web.pdf"/>
+    <hyperlink ref="D5" r:id="rId4" display="https://www.aicher-herbst-kultur.at/Aicher_Kirtag/"/>
+    <hyperlink ref="D6" r:id="rId5" display="https://www.tauroa.at/de/winterstellgut/"/>
+    <hyperlink ref="D7" r:id="rId6" display="https://www.salzburgerland.com/de/werfenweng/veranstaltungen/SBG/ff809fc9-ee1b-4036-82a1-35f154d0332f/werfenwenger-herbst-weis"/>
+    <hyperlink ref="D8" r:id="rId7" display="https://www.gde-schwarzach.salzburg.at/Seniorenzentrum_Schwarzach"/>
+    <hyperlink ref="D10" r:id="rId8" display="https://www.salzburgervolksliedwerk.at/termine/detail?tx_calendarize_calendar%5Baction%5D=detail&amp;tx_calendarize_calendar%5Bcontroller%5D=Calendar&amp;tx_calendarize_calendar%5Bindex%5D=103822&amp;cHash=3b0ade89f12374e9bdde86e47b10ff89"/>
+    <hyperlink ref="D12" r:id="rId9" display="https://www.dachstein.at/de/aktuelles/events/alm-musi-roas"/>
+    <hyperlink ref="D25" r:id="rId10" display="https://www.dachstein.at/de/aktuelles/events/alm-musi-roas "/>
+    <hyperlink ref="D27" r:id="rId11" display="https://zellamsee.kiwanis.at/veranstaltungen/ "/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>